--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104662_W23.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104662_W23.xlsx
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.2058</v>
+        <v>5.1992</v>
       </c>
       <c r="E2" t="n">
-        <v>2.4144</v>
+        <v>3.0304</v>
       </c>
       <c r="F2" t="n">
-        <v>1.7914</v>
+        <v>2.1688</v>
       </c>
       <c r="G2" t="n">
-        <v>4.3965</v>
+        <v>4.3982</v>
       </c>
       <c r="H2" t="n">
-        <v>1.4963</v>
+        <v>1.4964</v>
       </c>
       <c r="I2" t="n">
-        <v>2.9001</v>
+        <v>2.9018</v>
       </c>
       <c r="J2" t="n">
-        <v>2.5503</v>
+        <v>2.5168</v>
       </c>
       <c r="K2" t="n">
-        <v>1.7348</v>
+        <v>1.713</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8156</v>
+        <v>0.8038999999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>1.8461</v>
+        <v>1.8814</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.2384</v>
+        <v>-0.2166</v>
       </c>
       <c r="O2" t="n">
-        <v>2.0846</v>
+        <v>2.098</v>
       </c>
       <c r="P2" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S2" t="n">
-        <v>-2.807</v>
+        <v>-1.8104</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.1644</v>
+        <v>-0.5044999999999999</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.6426</v>
+        <v>-1.306</v>
       </c>
       <c r="V2" t="n">
-        <v>1.0285</v>
+        <v>1.018</v>
       </c>
       <c r="W2" t="n">
-        <v>1.0285</v>
+        <v>1.018</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.7865</v>
+        <v>1.7956</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9013</v>
+        <v>0.9673</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8852</v>
+        <v>0.8283</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6146</v>
+        <v>0.6201</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.0145</v>
+        <v>-0.0116</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6291</v>
+        <v>0.6317</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0173</v>
+        <v>0.0172</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0173</v>
+        <v>0.0172</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5973000000000001</v>
+        <v>0.6028</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.0318</v>
+        <v>-0.0289</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6291</v>
+        <v>0.6317</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.3744</v>
+        <v>-0.3692</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2087</v>
+        <v>-0.1394</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1657</v>
+        <v>-0.2298</v>
       </c>
       <c r="V3" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W3" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -721,58 +721,58 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3298</v>
+        <v>0.9901</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5079</v>
+        <v>0.2092</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8219</v>
+        <v>0.7809</v>
       </c>
       <c r="G4" t="n">
-        <v>1.3382</v>
+        <v>1.3476</v>
       </c>
       <c r="H4" t="n">
-        <v>1.2769</v>
+        <v>1.2835</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0613</v>
+        <v>0.06419999999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5563</v>
+        <v>0.5416</v>
       </c>
       <c r="K4" t="n">
-        <v>1.42</v>
+        <v>1.4134</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.8637</v>
+        <v>-0.8718</v>
       </c>
       <c r="M4" t="n">
-        <v>0.782</v>
+        <v>0.806</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.1431</v>
+        <v>-0.13</v>
       </c>
       <c r="O4" t="n">
-        <v>0.925</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="P4" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.5963</v>
+        <v>-1.951</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0484</v>
+        <v>-0.3324</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.5479</v>
+        <v>-1.6185</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0086</v>
+        <v>0.6624</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2804</v>
+        <v>0.0319</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7282999999999999</v>
+        <v>0.6304999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.017</v>
+        <v>-0.0116</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6867</v>
+        <v>0.6946</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.7037</v>
+        <v>-0.7062</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2592</v>
+        <v>0.2458</v>
       </c>
       <c r="K5" t="n">
-        <v>1.1602</v>
+        <v>1.1549</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.901</v>
+        <v>-0.909</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2762</v>
+        <v>-0.2574</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.4735</v>
+        <v>-0.4603</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1973</v>
+        <v>0.2028</v>
       </c>
       <c r="P5" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4676</v>
+        <v>-0.8316</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0212</v>
+        <v>-0.214</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4888</v>
+        <v>-0.6176</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="6">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6405999999999999</v>
+        <v>0.622</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.2143</v>
+        <v>-1.2454</v>
       </c>
       <c r="F6" t="n">
-        <v>1.8549</v>
+        <v>1.8675</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.3491</v>
+        <v>-0.3356</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4025</v>
+        <v>-0.4048</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0534</v>
+        <v>0.0692</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.1562</v>
+        <v>-0.1828</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.3055</v>
+        <v>-0.3317</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1493</v>
+        <v>0.1489</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1929</v>
+        <v>-0.1528</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.09710000000000001</v>
+        <v>-0.0731</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0958</v>
+        <v>-0.07969999999999999</v>
       </c>
       <c r="P6" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6681</v>
+        <v>-0.7025</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4476</v>
+        <v>-0.4465</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2205</v>
+        <v>-0.256</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.6105</v>
+        <v>-0.6162</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.6105</v>
+        <v>-0.6162</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3726</v>
+        <v>0.1975</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2354</v>
+        <v>-0.14</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1372</v>
+        <v>0.3375</v>
       </c>
       <c r="G7" t="n">
-        <v>0.797</v>
+        <v>0.7972</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1919</v>
+        <v>0.1924</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6051</v>
+        <v>0.6048</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5219</v>
+        <v>0.5086000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1141</v>
+        <v>0.1067</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4078</v>
+        <v>0.4019</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2751</v>
+        <v>0.2886</v>
       </c>
       <c r="N7" t="n">
-        <v>0.07779999999999999</v>
+        <v>0.0857</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1973</v>
+        <v>0.2028</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0653</v>
+        <v>-0.2323</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5263</v>
+        <v>0.174</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5916</v>
+        <v>-0.4063</v>
       </c>
       <c r="V7" t="n">
-        <v>0.3214</v>
+        <v>0.3155</v>
       </c>
       <c r="W7" t="n">
-        <v>0.3214</v>
+        <v>0.3155</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.6468</v>
+        <v>-0.3948</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.4809</v>
+        <v>-0.6423</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1659</v>
+        <v>0.2475</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6046</v>
+        <v>0.6133999999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3869</v>
+        <v>-0.3741</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9915</v>
+        <v>0.9874000000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8326</v>
+        <v>0.8099</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.3534</v>
+        <v>-0.3587</v>
       </c>
       <c r="L8" t="n">
-        <v>1.186</v>
+        <v>1.1686</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.228</v>
+        <v>-0.1965</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0335</v>
+        <v>-0.0154</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.1945</v>
+        <v>-0.1811</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R8" t="n">
-        <v>2.9488</v>
+        <v>2.9592</v>
       </c>
       <c r="S8" t="n">
-        <v>-2.0512</v>
+        <v>-1.8001</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2571</v>
+        <v>-0.3743</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.7941</v>
+        <v>-1.4257</v>
       </c>
       <c r="V8" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="W8" t="n">
-        <v>2.3461</v>
+        <v>2.3367</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="9">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.6878</v>
+        <v>-1.8717</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.5161</v>
+        <v>-2.3439</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8283</v>
+        <v>0.4723</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5788</v>
+        <v>0.5891999999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6001</v>
+        <v>0.6084000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.0213</v>
+        <v>-0.0193</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1514</v>
+        <v>0.1439</v>
       </c>
       <c r="K9" t="n">
-        <v>0.9005</v>
+        <v>0.8963</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.749</v>
+        <v>-0.7524</v>
       </c>
       <c r="M9" t="n">
-        <v>0.4274</v>
+        <v>0.4452</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3003</v>
+        <v>-0.2879</v>
       </c>
       <c r="O9" t="n">
-        <v>0.7277</v>
+        <v>0.7331</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.8147</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0944</v>
+        <v>-0.095</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3992</v>
+        <v>-0.2115</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4936</v>
+        <v>0.1165</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.0419</v>
+        <v>-3.105</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.6382</v>
+        <v>-1.6794</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.4037</v>
+        <v>-1.4256</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.8021</v>
+        <v>-1.8013</v>
       </c>
       <c r="H10" t="n">
-        <v>0.7301</v>
+        <v>0.7295</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.5322</v>
+        <v>-2.5308</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.7292</v>
+        <v>-0.7586000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>0.9209000000000001</v>
+        <v>0.9028</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.6501</v>
+        <v>-1.6614</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.0729</v>
+        <v>-1.0426</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1908</v>
+        <v>-0.1733</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.8822</v>
+        <v>-0.8694</v>
       </c>
       <c r="P10" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R10" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6708</v>
+        <v>-0.7363</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2571</v>
+        <v>-0.2559</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4138</v>
+        <v>-0.4804</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.7032</v>
+        <v>-1.7057</v>
       </c>
       <c r="W10" t="n">
-        <v>0.4822</v>
+        <v>0.4733</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="11">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.6003</v>
+        <v>-3.5618</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.0221</v>
+        <v>-2.9427</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.5780999999999999</v>
+        <v>-0.6191</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.0275</v>
+        <v>-1.0317</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.4269</v>
+        <v>-2.4351</v>
       </c>
       <c r="I11" t="n">
-        <v>1.3994</v>
+        <v>1.4034</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3255</v>
+        <v>0.3008</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.4657</v>
+        <v>-1.4866</v>
       </c>
       <c r="L11" t="n">
-        <v>1.7912</v>
+        <v>1.7874</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.353</v>
+        <v>-1.3325</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.9612000000000001</v>
+        <v>-0.9485</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.3918</v>
+        <v>-0.384</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.8147</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R11" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1476</v>
+        <v>-0.0929</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4688</v>
+        <v>-0.351</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3212</v>
+        <v>0.2581</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.6105</v>
+        <v>-0.6162</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.6105</v>
+        <v>-0.6162</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.4712</v>
+        <v>-5.2769</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.6453</v>
+        <v>-4.369</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.8258</v>
+        <v>-0.9079</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.7586</v>
+        <v>-2.7427</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.2282</v>
+        <v>-2.2124</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.5304</v>
+        <v>-0.5303</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.8467</v>
+        <v>-0.8658</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.3534</v>
+        <v>-0.3587</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.4932</v>
+        <v>-0.5071</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.9119</v>
+        <v>-1.8769</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.8747</v>
+        <v>-1.8536</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.0372</v>
+        <v>-0.0232</v>
       </c>
       <c r="P12" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R12" t="n">
-        <v>2.722</v>
+        <v>2.7316</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.0736</v>
+        <v>-1.9</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.5303</v>
+        <v>-1.2269</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5432</v>
+        <v>-0.6731</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.1041</v>
+        <v>-4.743399999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>-9.177499999999998</v>
+        <v>-9.123899999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>4.0737</v>
+        <v>4.380700000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>2.3754</v>
+        <v>2.4428</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.4770000000000003</v>
+        <v>-0.4332000000000003</v>
       </c>
       <c r="I13" t="n">
-        <v>2.852300000000001</v>
+        <v>2.8759</v>
       </c>
       <c r="J13" t="n">
-        <v>3.4824</v>
+        <v>3.2774</v>
       </c>
       <c r="K13" t="n">
-        <v>3.7898</v>
+        <v>3.6686</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.3071000000000001</v>
+        <v>-0.3909999999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.106999999999999</v>
+        <v>-0.8347000000000002</v>
       </c>
       <c r="N13" t="n">
-        <v>-4.2666</v>
+        <v>-4.1019</v>
       </c>
       <c r="O13" t="n">
-        <v>3.159500000000001</v>
+        <v>3.267</v>
       </c>
       <c r="P13" t="n">
-        <v>4.5366</v>
+        <v>4.552600000000001</v>
       </c>
       <c r="Q13" t="n">
-        <v>-12.4758</v>
+        <v>-12.5198</v>
       </c>
       <c r="R13" t="n">
-        <v>17.0125</v>
+        <v>17.0725</v>
       </c>
       <c r="S13" t="n">
-        <v>-10.8275</v>
+        <v>-10.5213</v>
       </c>
       <c r="T13" t="n">
-        <v>-4.2341</v>
+        <v>-3.8824</v>
       </c>
       <c r="U13" t="n">
-        <v>-6.5934</v>
+        <v>-6.6388</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.1886</v>
+        <v>-1.2176</v>
       </c>
       <c r="W13" t="n">
-        <v>4.0499</v>
+        <v>4.000599999999999</v>
       </c>
       <c r="X13" t="n">
-        <v>-5.2384</v>
+        <v>-5.218100000000001</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.5054</v>
+        <v>3.9505</v>
       </c>
       <c r="E14" t="n">
-        <v>4.8117</v>
+        <v>3.0067</v>
       </c>
       <c r="F14" t="n">
-        <v>1.6936</v>
+        <v>0.9437</v>
       </c>
       <c r="G14" t="n">
-        <v>0.007</v>
+        <v>-0.0066</v>
       </c>
       <c r="H14" t="n">
-        <v>1.3984</v>
+        <v>1.3878</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.3914</v>
+        <v>-1.3944</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.1777</v>
+        <v>-0.2098</v>
       </c>
       <c r="K14" t="n">
-        <v>1.5097</v>
+        <v>1.4889</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.6874</v>
+        <v>-1.6987</v>
       </c>
       <c r="M14" t="n">
-        <v>0.1847</v>
+        <v>0.2032</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.1113</v>
+        <v>-0.1011</v>
       </c>
       <c r="O14" t="n">
-        <v>0.2959</v>
+        <v>0.3043</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R14" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S14" t="n">
-        <v>5.7933</v>
+        <v>3.253</v>
       </c>
       <c r="T14" t="n">
-        <v>3.7776</v>
+        <v>2.018</v>
       </c>
       <c r="U14" t="n">
-        <v>2.0158</v>
+        <v>1.235</v>
       </c>
       <c r="V14" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.9317</v>
       </c>
       <c r="W14" t="n">
-        <v>2.3461</v>
+        <v>2.3367</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.4141</v>
+        <v>-1.405</v>
       </c>
     </row>
     <row r="15">
@@ -1579,58 +1579,58 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.9794</v>
+        <v>2.1208</v>
       </c>
       <c r="E15" t="n">
-        <v>2.721</v>
+        <v>0.8077</v>
       </c>
       <c r="F15" t="n">
-        <v>1.2584</v>
+        <v>1.3131</v>
       </c>
       <c r="G15" t="n">
-        <v>2.0183</v>
+        <v>2.0141</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9467</v>
+        <v>0.9368</v>
       </c>
       <c r="I15" t="n">
-        <v>1.0716</v>
+        <v>1.0772</v>
       </c>
       <c r="J15" t="n">
-        <v>2.5214</v>
+        <v>2.4991</v>
       </c>
       <c r="K15" t="n">
-        <v>1.2153</v>
+        <v>1.1958</v>
       </c>
       <c r="L15" t="n">
-        <v>1.3061</v>
+        <v>1.3033</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.503</v>
+        <v>-0.4851</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.2685</v>
+        <v>-0.259</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.2345</v>
+        <v>-0.226</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S15" t="n">
-        <v>2.6416</v>
+        <v>0.7896</v>
       </c>
       <c r="T15" t="n">
-        <v>2.468</v>
+        <v>0.5849</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1736</v>
+        <v>0.2047</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. ARANITOVIC</t>
+          <t>M. ANDRIC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.2427</v>
+        <v>2.0592</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.2477</v>
+        <v>1.442</v>
       </c>
       <c r="F16" t="n">
-        <v>3.4904</v>
+        <v>0.6172</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.7816</v>
+        <v>2.8459</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.2005</v>
+        <v>-0.5054999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5810999999999999</v>
+        <v>3.3513</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.7355</v>
+        <v>3.5887</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.5062</v>
+        <v>-0.0452</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.2293</v>
+        <v>3.6339</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.0461</v>
+        <v>-0.7428</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6944</v>
+        <v>-0.4603</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.3517</v>
+        <v>-0.2826</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9073</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.361</v>
+        <v>-2.2763</v>
       </c>
       <c r="R16" t="n">
-        <v>2.2683</v>
+        <v>1.8211</v>
       </c>
       <c r="S16" t="n">
-        <v>2.2777</v>
+        <v>0.4575</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1512</v>
+        <v>0.1297</v>
       </c>
       <c r="U16" t="n">
-        <v>2.4289</v>
+        <v>0.3278</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.1607</v>
+        <v>-0.7887999999999999</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.1607</v>
+        <v>-0.7887999999999999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. ANDRIC</t>
+          <t>A. ARANITOVIC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5123</v>
+        <v>1.3912</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5352</v>
+        <v>-1.3307</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.0229</v>
+        <v>2.7219</v>
       </c>
       <c r="G17" t="n">
-        <v>2.8535</v>
+        <v>-1.7784</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.505</v>
+        <v>-1.2005</v>
       </c>
       <c r="I17" t="n">
-        <v>3.3585</v>
+        <v>-0.5778</v>
       </c>
       <c r="J17" t="n">
-        <v>3.6201</v>
+        <v>-0.7633</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.0315</v>
+        <v>-0.5246</v>
       </c>
       <c r="L17" t="n">
-        <v>3.6516</v>
+        <v>-0.2388</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.7665999999999999</v>
+        <v>-1.015</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.4735</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.2931</v>
+        <v>-0.3391</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.4537</v>
+        <v>0.9105</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.2683</v>
+        <v>-1.3658</v>
       </c>
       <c r="R17" t="n">
-        <v>1.8147</v>
+        <v>2.2763</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.084</v>
+        <v>2.4168</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8166</v>
+        <v>0.7984</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2674</v>
+        <v>1.6184</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.8036</v>
+        <v>-0.1578</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.8036</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="18">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4931</v>
+        <v>1.1517</v>
       </c>
       <c r="E18" t="n">
-        <v>1.6297</v>
+        <v>1.8529</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.1366</v>
+        <v>-0.7012</v>
       </c>
       <c r="G18" t="n">
-        <v>1.77</v>
+        <v>1.7765</v>
       </c>
       <c r="H18" t="n">
-        <v>1.2769</v>
+        <v>1.2835</v>
       </c>
       <c r="I18" t="n">
         <v>0.4931</v>
       </c>
       <c r="J18" t="n">
-        <v>2.289</v>
+        <v>2.276</v>
       </c>
       <c r="K18" t="n">
-        <v>1.2468</v>
+        <v>1.2411</v>
       </c>
       <c r="L18" t="n">
-        <v>1.0422</v>
+        <v>1.035</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.5189</v>
+        <v>-0.4995</v>
       </c>
       <c r="N18" t="n">
-        <v>0.0301</v>
+        <v>0.0424</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.549</v>
+        <v>-0.5419</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.9308999999999999</v>
+        <v>-0.2881</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6593</v>
+        <v>-0.4231</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2716</v>
+        <v>0.135</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="19">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4804</v>
+        <v>0.5692</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.0712</v>
+        <v>-0.4448</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5516</v>
+        <v>1.014</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.073</v>
+        <v>-1.0751</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.9104</v>
+        <v>-0.9159</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1626</v>
+        <v>-0.1592</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.2845</v>
+        <v>-1.3059</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.6101</v>
+        <v>-0.628</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6744</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="M19" t="n">
-        <v>0.2115</v>
+        <v>0.2308</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.3003</v>
+        <v>-0.2879</v>
       </c>
       <c r="O19" t="n">
-        <v>0.5118</v>
+        <v>0.5187</v>
       </c>
       <c r="P19" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R19" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S19" t="n">
-        <v>1.0997</v>
+        <v>1.1891</v>
       </c>
       <c r="T19" t="n">
-        <v>1.2794</v>
+        <v>0.931</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1797</v>
+        <v>0.2581</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. APIC</t>
+          <t>D. MAVRA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.5528</v>
+        <v>0.1047</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3508</v>
+        <v>-1.6461</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.9036</v>
+        <v>1.7508</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.3781</v>
+        <v>0.1471</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3781</v>
+        <v>2.3927</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>-2.2456</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>0.1451</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>2.5371</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>-2.3919</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.3781</v>
+        <v>0.0019</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.3781</v>
+        <v>-0.1444</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>0.1463</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.2268</v>
+        <v>-2.9592</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.2268</v>
+        <v>-3.6421</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>0.6829</v>
       </c>
       <c r="S20" t="n">
-        <v>0.5985</v>
+        <v>1.2112</v>
       </c>
       <c r="T20" t="n">
-        <v>0.5777</v>
+        <v>0.7614</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0209</v>
+        <v>0.4498</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.5463</v>
+        <v>1.7057</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.5463</v>
+        <v>0.6162</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. MAVRA</t>
+          <t>F. ALONSO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.6875</v>
+        <v>-0.7042</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.0638</v>
+        <v>-2.6087</v>
       </c>
       <c r="F21" t="n">
-        <v>1.3763</v>
+        <v>1.9045</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1683</v>
+        <v>-4.0459</v>
       </c>
       <c r="H21" t="n">
-        <v>2.3968</v>
+        <v>-2.9121</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.2285</v>
+        <v>-1.1338</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1886</v>
+        <v>-3.9624</v>
       </c>
       <c r="K21" t="n">
-        <v>2.5558</v>
+        <v>-2.1071</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.3672</v>
+        <v>-1.8553</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.0203</v>
+        <v>-0.0835</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.159</v>
+        <v>-0.805</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1387</v>
+        <v>0.7215</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.9488</v>
+        <v>0.4553</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.6293</v>
+        <v>-1.3658</v>
       </c>
       <c r="R21" t="n">
-        <v>0.6805</v>
+        <v>1.8211</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3899</v>
+        <v>2.1124</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2843</v>
+        <v>1.63</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1055</v>
+        <v>0.4824</v>
       </c>
       <c r="V21" t="n">
-        <v>1.7032</v>
+        <v>0.7739</v>
       </c>
       <c r="W21" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X21" t="n">
-        <v>0.6105</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>F. ALONSO</t>
+          <t>D. APIC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.9834</v>
+        <v>-0.987</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.7552</v>
+        <v>-0.1209</v>
       </c>
       <c r="F22" t="n">
-        <v>1.7717</v>
+        <v>-0.8661</v>
       </c>
       <c r="G22" t="n">
-        <v>-4.0392</v>
+        <v>-0.3736</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.9089</v>
+        <v>-0.3736</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.1302</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>-3.9285</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.0891</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.8393</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.1107</v>
+        <v>-0.3736</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.8198</v>
+        <v>-0.3736</v>
       </c>
       <c r="O22" t="n">
-        <v>0.7091</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>0.4537</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.361</v>
+        <v>-0.2276</v>
       </c>
       <c r="R22" t="n">
-        <v>1.8147</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0.8308</v>
+        <v>0.159</v>
       </c>
       <c r="T22" t="n">
-        <v>0.4416</v>
+        <v>0.1067</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3892</v>
+        <v>0.0523</v>
       </c>
       <c r="V22" t="n">
-        <v>0.7712</v>
+        <v>-0.5447</v>
       </c>
       <c r="W22" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.3214</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="23">
@@ -2203,64 +2203,64 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.8854</v>
+        <v>-3.7747</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.984</v>
+        <v>-5.3388</v>
       </c>
       <c r="F23" t="n">
-        <v>1.0987</v>
+        <v>1.5641</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.9207</v>
+        <v>-1.9467</v>
       </c>
       <c r="H23" t="n">
-        <v>0.3611</v>
+        <v>0.3401</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.2817</v>
+        <v>-2.2868</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.3858</v>
+        <v>-1.4328</v>
       </c>
       <c r="K23" t="n">
-        <v>0.976</v>
+        <v>0.9438</v>
       </c>
       <c r="L23" t="n">
-        <v>-2.3618</v>
+        <v>-2.3766</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.5348000000000001</v>
+        <v>-0.5139</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.6149</v>
+        <v>-0.6037</v>
       </c>
       <c r="O23" t="n">
-        <v>0.08</v>
+        <v>0.0898</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.722</v>
+        <v>-2.7316</v>
       </c>
       <c r="Q23" t="n">
-        <v>-4.5367</v>
+        <v>-4.5526</v>
       </c>
       <c r="R23" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.7891</v>
+        <v>0.3589</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6079</v>
+        <v>0.1019</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1812</v>
+        <v>0.257</v>
       </c>
       <c r="V23" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="W23" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>5.1042</v>
+        <v>5.881399999999998</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.073500000000001</v>
+        <v>-4.380699999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>9.177600000000002</v>
+        <v>10.262</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.3755</v>
+        <v>-2.4427</v>
       </c>
       <c r="H24" t="n">
-        <v>0.4769999999999999</v>
+        <v>0.4332999999999998</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.8523</v>
+        <v>-2.876</v>
       </c>
       <c r="J24" t="n">
-        <v>1.107099999999999</v>
+        <v>0.8346999999999982</v>
       </c>
       <c r="K24" t="n">
-        <v>4.266699999999999</v>
+        <v>4.101800000000001</v>
       </c>
       <c r="L24" t="n">
-        <v>-3.1595</v>
+        <v>-3.267</v>
       </c>
       <c r="M24" t="n">
-        <v>-3.4823</v>
+        <v>-3.2775</v>
       </c>
       <c r="N24" t="n">
-        <v>-3.7897</v>
+        <v>-3.6685</v>
       </c>
       <c r="O24" t="n">
-        <v>0.3071999999999999</v>
+        <v>0.391</v>
       </c>
       <c r="P24" t="n">
-        <v>-4.5366</v>
+        <v>-4.5526</v>
       </c>
       <c r="Q24" t="n">
-        <v>-17.0124</v>
+        <v>-17.0723</v>
       </c>
       <c r="R24" t="n">
-        <v>12.4758</v>
+        <v>12.5198</v>
       </c>
       <c r="S24" t="n">
-        <v>10.8275</v>
+        <v>11.6594</v>
       </c>
       <c r="T24" t="n">
-        <v>6.593599999999999</v>
+        <v>6.6389</v>
       </c>
       <c r="U24" t="n">
-        <v>4.234</v>
+        <v>5.020499999999999</v>
       </c>
       <c r="V24" t="n">
-        <v>1.1887</v>
+        <v>1.2175</v>
       </c>
       <c r="W24" t="n">
-        <v>5.2385</v>
+        <v>5.2182</v>
       </c>
       <c r="X24" t="n">
-        <v>-4.0497</v>
+        <v>-4.000599999999999</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104662_W23.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104662_W23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104662_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104662_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104662_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104662_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104662_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104662_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104662_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104662_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104662_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>0</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104662_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104662_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-5.218100000000001</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-1.405</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104662_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104662_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-0.7887999999999999</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104662_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104662_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104662_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104662_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0.6162</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104662_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104662_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104662_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>0</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104662_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,7 @@
       <c r="X24" t="n">
         <v>-4.000599999999999</v>
       </c>
+      <c r="Y24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
